--- a/assets/downloads/CONFIG MAKER by KJ.xlsx
+++ b/assets/downloads/CONFIG MAKER by KJ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/kevin_jamet_epita_fr/Documents/Others/Configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="909" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{118AC626-676F-47C4-B55C-EA11C5BB37C5}"/>
+  <xr:revisionPtr revIDLastSave="941" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A877D3BE-3E5B-4EF9-A0BA-64457C001F9E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8947F335-7243-4BC9-9D88-00188AB47FC0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>En stock</t>
   </si>
@@ -101,9 +101,6 @@
     <t>SETUP</t>
   </si>
   <si>
-    <t>OPT</t>
-  </si>
-  <si>
     <t>TOTAUX</t>
   </si>
   <si>
@@ -158,19 +155,31 @@
     <t>Tapis de Souris</t>
   </si>
   <si>
-    <t>CONFIG MAKER 2024.7.18</t>
-  </si>
-  <si>
     <t>Econom.</t>
   </si>
   <si>
     <t>by KJ</t>
   </si>
   <si>
-    <t>https://kevinjmt.github.io/</t>
-  </si>
-  <si>
     <t>CONFIG MAKER v2024.7.18</t>
+  </si>
+  <si>
+    <t>NOM DE LA CONFIG</t>
+  </si>
+  <si>
+    <t>TÉLÉCHARGER DE NOUVEAU</t>
+  </si>
+  <si>
+    <t>Système d'exploitation</t>
+  </si>
+  <si>
+    <t>OPT4</t>
+  </si>
+  <si>
+    <t>OPT5</t>
+  </si>
+  <si>
+    <t>OPTS</t>
   </si>
 </sst>
 </file>
@@ -350,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -389,18 +398,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -437,10 +437,18 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -496,39 +504,43 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$17" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$18" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$25" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$29" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
+<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$30" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$29" max="100" page="10" val="0"/>
+<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$13" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1373,13 +1385,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1423,13 +1435,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1473,13 +1485,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1521,13 +1533,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1566,13 +1578,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1611,13 +1623,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1656,13 +1668,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1701,13 +1713,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1748,13 +1760,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1798,13 +1810,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>6350</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1848,13 +1860,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1898,13 +1910,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1948,13 +1960,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2048,13 +2060,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>6350</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2098,13 +2110,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2115,7 +2127,7 @@
                   <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF05DDB2-85C3-4BB8-9FD4-07AAD791CC4B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2148,13 +2160,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2165,7 +2177,7 @@
                   <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F4EF56E-383E-4320-9F39-6145B0BFE515}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2198,13 +2210,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2215,7 +2227,7 @@
                   <a14:compatExt spid="_x0000_s1093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E77C7349-EFE3-4018-9F49-A2FFA4301659}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2248,13 +2260,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2265,7 +2277,7 @@
                   <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6157F137-9EEC-4584-A95E-3586551A9293}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2298,13 +2310,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2315,7 +2327,57 @@
                   <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F09B882-0A12-4ECE-8B0F-67E5CB638A75}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1096" name="Spinner 72" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1096"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2666,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF3D32E-9FFB-480D-9074-7649C0A05B73}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.81640625" customWidth="1"/>
@@ -2681,30 +2743,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="A1" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29">
+      <c r="B2" s="27"/>
+      <c r="C2" s="28">
         <v>45491</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -2735,658 +2797,679 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="13"/>
-      <c r="B4" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="32">
-        <v>0</v>
-      </c>
-      <c r="F4" s="32">
-        <v>0</v>
-      </c>
-      <c r="G4" s="32">
-        <v>0</v>
-      </c>
-      <c r="H4" s="32">
+      <c r="B4" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16">
+        <v>0</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0</v>
+      </c>
+      <c r="H4" s="16">
         <f>(E4*F4)+G4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="13"/>
-      <c r="B5" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <v>0</v>
-      </c>
-      <c r="F5" s="32">
-        <v>0</v>
-      </c>
-      <c r="G5" s="32">
-        <v>0</v>
-      </c>
-      <c r="H5" s="32">
-        <f t="shared" ref="H5:H12" si="0">(E5*F5)+G5</f>
+      <c r="B5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="16">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <f t="shared" ref="H5:H13" si="0">(E5*F5)+G5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="13"/>
-      <c r="B6" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32">
-        <v>0</v>
-      </c>
-      <c r="F6" s="32">
-        <v>0</v>
-      </c>
-      <c r="G6" s="32">
-        <v>0</v>
-      </c>
-      <c r="H6" s="32">
+      <c r="B6" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="16">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="13"/>
-      <c r="B7" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32">
-        <v>0</v>
-      </c>
-      <c r="F7" s="32">
-        <v>0</v>
-      </c>
-      <c r="G7" s="32">
-        <v>0</v>
-      </c>
-      <c r="H7" s="32">
+      <c r="B7" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>
-      <c r="B8" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32">
-        <v>0</v>
-      </c>
-      <c r="F8" s="32">
-        <v>0</v>
-      </c>
-      <c r="G8" s="32">
-        <v>0</v>
-      </c>
-      <c r="H8" s="32">
+      <c r="B8" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16">
+        <v>0</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32">
-        <v>0</v>
-      </c>
-      <c r="F9" s="32">
-        <v>0</v>
-      </c>
-      <c r="G9" s="32">
-        <v>0</v>
-      </c>
-      <c r="H9" s="32">
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="16">
+        <v>0</v>
+      </c>
+      <c r="F9" s="16">
+        <v>0</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>
-      <c r="B10" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32">
-        <v>0</v>
-      </c>
-      <c r="F10" s="32">
-        <v>0</v>
-      </c>
-      <c r="G10" s="32">
-        <v>0</v>
-      </c>
-      <c r="H10" s="32">
+      <c r="B10" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16">
+        <v>0</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>
-      <c r="B11" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32">
-        <v>0</v>
-      </c>
-      <c r="F11" s="32">
-        <v>0</v>
-      </c>
-      <c r="G11" s="32">
-        <v>0</v>
-      </c>
-      <c r="H11" s="32">
+      <c r="B11" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>
-      <c r="B12" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32">
-        <v>0</v>
-      </c>
-      <c r="F12" s="32">
-        <v>0</v>
-      </c>
-      <c r="G12" s="32">
-        <v>0</v>
-      </c>
-      <c r="H12" s="32">
+      <c r="B12" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="20" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="13"/>
+      <c r="B13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32">
-        <v>0</v>
-      </c>
-      <c r="F16" s="32">
-        <v>0</v>
-      </c>
-      <c r="G16" s="32">
-        <v>0</v>
-      </c>
-      <c r="H16" s="32">
-        <f>(E16*F16)+G16</f>
-        <v>0</v>
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
-      <c r="B17" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32">
-        <v>0</v>
-      </c>
-      <c r="F17" s="32">
-        <v>0</v>
-      </c>
-      <c r="G17" s="32">
-        <v>0</v>
-      </c>
-      <c r="H17" s="32">
+      <c r="B17" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="16">
+        <v>0</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0</v>
+      </c>
+      <c r="G17" s="16">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16">
+        <f>(E17*F17)+G17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>
-      <c r="B18" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32">
-        <v>0</v>
-      </c>
-      <c r="F18" s="32">
-        <v>0</v>
-      </c>
-      <c r="G18" s="32">
-        <v>0</v>
-      </c>
-      <c r="H18" s="32">
-        <f t="shared" ref="H18:H21" si="1">(E18*F18)+G18</f>
+      <c r="B18" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="16">
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>
-      <c r="B19" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32">
-        <v>0</v>
-      </c>
-      <c r="F19" s="32">
-        <v>0</v>
-      </c>
-      <c r="G19" s="32">
-        <v>0</v>
-      </c>
-      <c r="H19" s="32">
+      <c r="B19" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="16">
+        <v>0</v>
+      </c>
+      <c r="F19" s="16">
+        <v>0</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <f t="shared" ref="H19:H22" si="1">(E19*F19)+G19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
-      <c r="B20" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32">
-        <v>0</v>
-      </c>
-      <c r="F20" s="32">
-        <v>0</v>
-      </c>
-      <c r="G20" s="32">
-        <v>0</v>
-      </c>
-      <c r="H20" s="32">
-        <f t="shared" si="1"/>
+      <c r="B20" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16">
+        <v>0</v>
+      </c>
+      <c r="F20" s="16">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0</v>
+      </c>
+      <c r="H20" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
-      <c r="B21" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32">
-        <v>0</v>
-      </c>
-      <c r="F21" s="32">
-        <v>0</v>
-      </c>
-      <c r="G21" s="32">
-        <v>0</v>
-      </c>
-      <c r="H21" s="32">
+      <c r="B21" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="16">
+        <v>0</v>
+      </c>
+      <c r="F21" s="16">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="20" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="13"/>
+      <c r="B22" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="16">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="32">
-        <v>0</v>
-      </c>
-      <c r="F25" s="34">
-        <v>0</v>
-      </c>
-      <c r="G25" s="32">
-        <v>0</v>
-      </c>
-      <c r="H25" s="32">
-        <f>(E25*F25)+G25</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="35">
-        <f>H25-H4</f>
-        <v>0</v>
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>
-      <c r="B26" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32">
-        <v>0</v>
-      </c>
-      <c r="F26" s="32">
-        <v>0</v>
-      </c>
-      <c r="G26" s="32">
-        <v>0</v>
-      </c>
-      <c r="H26" s="32">
+      <c r="B26" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="16">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="16">
+        <v>0</v>
+      </c>
+      <c r="H26" s="16">
         <f>(E26*F26)+G26</f>
         <v>0</v>
       </c>
-      <c r="I26" s="35">
-        <f>H26-H10</f>
+      <c r="I26" s="18">
+        <f>H26-H4</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
-      <c r="B27" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32">
-        <v>0</v>
-      </c>
-      <c r="F27" s="32">
-        <v>0</v>
-      </c>
-      <c r="G27" s="32">
-        <v>0</v>
-      </c>
-      <c r="H27" s="32">
-        <f t="shared" ref="H27" si="2">(E27*F27)+G27</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="35">
+      <c r="B27" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="17"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16">
+        <v>0</v>
+      </c>
+      <c r="F27" s="16">
+        <v>0</v>
+      </c>
+      <c r="G27" s="16">
+        <v>0</v>
+      </c>
+      <c r="H27" s="16">
+        <f>(E27*F27)+G27</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="18">
         <f>H27-H10</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
-      <c r="B28" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32">
-        <v>0</v>
-      </c>
-      <c r="F28" s="32">
-        <v>0</v>
-      </c>
-      <c r="G28" s="32">
-        <v>0</v>
-      </c>
-      <c r="H28" s="32">
-        <f t="shared" ref="H28" si="3">(E28*F28)+G28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="35">
-        <f>H28-H11</f>
+      <c r="B28" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16">
+        <v>0</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0</v>
+      </c>
+      <c r="H28" s="16">
+        <f t="shared" ref="H28" si="2">(E28*F28)+G28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="18">
+        <f>H28-H10</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
-      <c r="B29" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32">
-        <v>0</v>
-      </c>
-      <c r="F29" s="32">
-        <v>0</v>
-      </c>
-      <c r="G29" s="32">
-        <v>0</v>
-      </c>
-      <c r="H29" s="32">
-        <f t="shared" ref="H29" si="4">(E29*F29)+G29</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="35">
-        <f>H29-H12</f>
+      <c r="B29" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="17"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16">
+        <v>0</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0</v>
+      </c>
+      <c r="G29" s="16">
+        <v>0</v>
+      </c>
+      <c r="H29" s="16">
+        <f t="shared" ref="H29" si="3">(E29*F29)+G29</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="18">
+        <f>H29-H11</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C30" s="4"/>
-      <c r="I30" s="5"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16">
+        <v>0</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0</v>
+      </c>
+      <c r="G30" s="16">
+        <v>0</v>
+      </c>
+      <c r="H30" s="16">
+        <f t="shared" ref="H30" si="4">(E30*F30)+G30</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="18">
+        <f>H30-H12</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C31" s="4"/>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="F32" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="23"/>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C32" s="4"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="6">
-        <f>SUM(H4:H12)</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="19">
-        <f>B36-B37</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="19"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="H33" s="17"/>
-      <c r="I33" s="18"/>
+      <c r="A33" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="F33" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" s="6">
-        <f>SUM(H16:H21)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="H34" s="17"/>
-      <c r="I34" s="18"/>
+        <f>SUM(H4:H12)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="34">
+        <f>B37-B38</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="34"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="32"/>
+      <c r="I34" s="33"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" s="6">
-        <f>SUM(H25:H29)</f>
-        <v>0</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="H35" s="17"/>
-      <c r="I35" s="18"/>
+        <f>SUM(H17:H22)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="32"/>
+      <c r="I35" s="33"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="6">
+        <f>SUM(H26:H30)</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" s="32"/>
+      <c r="I36" s="33"/>
+    </row>
+    <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="3">
-        <f>B33+B34+B35</f>
-        <v>0</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="16" t="s">
+      <c r="B37" s="3">
+        <f>B34+B35+B36</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="18"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="33"/>
     </row>
-    <row r="37" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="6" t="s">
+    <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="6">
-        <v>0</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
+      <c r="B38" s="6">
+        <v>0</v>
+      </c>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
     </row>
-    <row r="38" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>42</v>
+    <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="15" t="s">
+    <row r="41" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="15" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="C33:D37"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C39" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>
-    <hyperlink ref="B40" r:id="rId2" xr:uid="{12A6037E-86C9-4725-89EE-1D861E2C5CBA}"/>
+    <hyperlink ref="C40" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>
+    <hyperlink ref="B41" r:id="rId2" xr:uid="{BB511D4F-6DFD-4166-91EE-2B5D78AF6761}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
@@ -3425,13 +3508,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>24</xdr:row>
+                    <xdr:row>25</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>25</xdr:row>
+                    <xdr:row>26</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3447,13 +3530,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>25</xdr:row>
+                    <xdr:row>26</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>26</xdr:row>
+                    <xdr:row>27</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3645,13 +3728,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>15</xdr:row>
+                    <xdr:row>16</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>16</xdr:row>
+                    <xdr:row>17</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3667,13 +3750,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>17</xdr:row>
+                    <xdr:row>18</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>18</xdr:row>
+                    <xdr:row>19</xdr:row>
                     <xdr:rowOff>6350</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3689,13 +3772,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>18</xdr:row>
+                    <xdr:row>19</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>19</xdr:row>
+                    <xdr:row>20</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3711,13 +3794,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>19</xdr:row>
+                    <xdr:row>20</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>20</xdr:row>
+                    <xdr:row>21</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3733,13 +3816,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>20</xdr:row>
+                    <xdr:row>21</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>21</xdr:row>
+                    <xdr:row>22</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3777,13 +3860,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>16</xdr:row>
+                    <xdr:row>17</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>17</xdr:row>
+                    <xdr:row>18</xdr:row>
                     <xdr:rowOff>6350</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3799,13 +3882,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>26</xdr:row>
+                    <xdr:row>27</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>27</xdr:row>
+                    <xdr:row>28</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3821,13 +3904,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>26</xdr:row>
+                    <xdr:row>27</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>27</xdr:row>
+                    <xdr:row>28</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3843,13 +3926,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>27</xdr:row>
+                    <xdr:row>28</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>28</xdr:row>
+                    <xdr:row>29</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3865,13 +3948,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>27</xdr:row>
+                    <xdr:row>28</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>28</xdr:row>
+                    <xdr:row>29</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3887,13 +3970,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>28</xdr:row>
+                    <xdr:row>29</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>29</xdr:row>
+                    <xdr:row>30</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3909,13 +3992,35 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>28</xdr:row>
+                    <xdr:row>29</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>29</xdr:row>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1096" r:id="rId30" name="Spinner 72">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>13</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/assets/downloads/CONFIG MAKER by KJ.xlsx
+++ b/assets/downloads/CONFIG MAKER by KJ.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/kevin_jamet_epita_fr/Documents/Others/Configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="941" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A877D3BE-3E5B-4EF9-A0BA-64457C001F9E}"/>
+  <xr:revisionPtr revIDLastSave="1214" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E9BE963-031D-4AC8-9EE5-52301470B6A1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8947F335-7243-4BC9-9D88-00188AB47FC0}"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIG 1" sheetId="1" r:id="rId1"/>
+    <sheet name="MANUEL" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="73">
   <si>
     <t>En stock</t>
   </si>
@@ -181,6 +182,81 @@
   <si>
     <t>OPTS</t>
   </si>
+  <si>
+    <t>MANUEL D'UTILISATION</t>
+  </si>
+  <si>
+    <t>Sur chaque ligne, renseigner:</t>
+  </si>
+  <si>
+    <t>La référence du produit</t>
+  </si>
+  <si>
+    <t>Le prix unitaire</t>
+  </si>
+  <si>
+    <t>Le lien vers un comparateur de prix</t>
+  </si>
+  <si>
+    <t>Si le produit est en stock</t>
+  </si>
+  <si>
+    <t>La quantité souhaitée</t>
+  </si>
+  <si>
+    <t>Les frais de livraison pour le produit</t>
+  </si>
+  <si>
+    <t>Le lien du site où le produit est le moins cher</t>
+  </si>
+  <si>
+    <t>⚠️ Pour les économies ⚠️</t>
+  </si>
+  <si>
+    <t>Sur chaque ligne, la formule est la suivante pour calculer les économies:</t>
+  </si>
+  <si>
+    <t>Prix total du PC</t>
+  </si>
+  <si>
+    <t>Prix total du Setup</t>
+  </si>
+  <si>
+    <t>Prix total des options choisies</t>
+  </si>
+  <si>
+    <t>Prix total</t>
+  </si>
+  <si>
+    <t>Budget Fixé</t>
+  </si>
+  <si>
+    <t>`=H26-0`</t>
+  </si>
+  <si>
+    <t>Pour calculer les économies, il suffit de remplacer le 0</t>
+  </si>
+  <si>
+    <t>par la case que vous souhaitez comparer. Par exemple:</t>
+  </si>
+  <si>
+    <t>Si OPT1 est un processeur, il suffit de mettre la case du prix total du</t>
+  </si>
+  <si>
+    <t>processeur (H4) à la place du 0. La nouvelle formule est donc:</t>
+  </si>
+  <si>
+    <t>`=H26-H4`</t>
+  </si>
+  <si>
+    <t>Il ne reste plus qu'à renseigner les informations au dessus!</t>
+  </si>
+  <si>
+    <t>Prix total comparé au budget fixé</t>
+  </si>
+  <si>
+    <t>Prix total du produit, quantité et livraison appliquée</t>
+  </si>
 </sst>
 </file>
 
@@ -189,7 +265,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[Red]\▲\ 0.00;[Green]\ \▼\ 0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,8 +325,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,8 +391,62 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -354,12 +506,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,6 +633,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -437,17 +681,94 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -472,47 +793,47 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$11" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$12" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$9" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$18" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,32 +860,132 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$13" max="100" page="10" val="0"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$10" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$11" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$12" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$9" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$18" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$29" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$30" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$13" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$10" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$11" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$10" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$12" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2407,6 +2828,1846 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Spinner 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61FB5EC9-F771-4B7C-A55C-237BAE44ADFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="933450"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Spinner 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1026"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C866209-3260-4185-8693-9387161461EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="1117600"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Spinner 3" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1027"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B10C7B63-5AD6-48C0-9D28-5335519348E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="1301750"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Spinner 4" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1028"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDC1279E-7E1D-4698-809E-1B9416F4595A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="1485900"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Spinner 5" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1029"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{984C00EA-6C19-4288-96E1-EB0AD3C81C28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="2038350"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Spinner 6" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1030"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{153DEF4E-B7E5-412D-8A32-DD74AF9C9EA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="1670050"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Spinner 7" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1031"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBF7788E-BFD3-46A7-837B-348745FE4736}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="2222500"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Spinner 8" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1032"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAB7DCDA-D72E-4BD0-9782-15756A480B9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="2406650"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3073" name="Spinner 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54289062-98E0-45D0-A26D-D866DC5C8188}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3074" name="Spinner 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D82B1CAB-137A-44A7-A8F9-648A63FE8EB7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>6350</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3075" name="Spinner 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D314E8DF-357B-4856-8E54-B73378E08F68}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3076" name="Spinner 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C75111DE-F527-4375-9E0A-8E0B5B9ADECA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3077" name="Spinner 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C97EE75-F7E8-4E78-86F1-411B4A51A5B9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3078" name="Spinner 6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D69533A8-1F6B-42A5-847A-287A5C67DAB0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3079" name="Spinner 7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7942FBE8-149D-4C22-B6D1-E2BD07CDC689}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3080" name="Spinner 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42AD6690-5C19-4AE4-8C84-227443DE9D4A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3081" name="Spinner 9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BDCECBC-150A-4C3B-9367-D1AC7741F971}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3082" name="Spinner 10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EACE3175-F8E0-41D3-8A5C-82BBA8E16570}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3083" name="Spinner 11" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6EA0CA8-A7B6-47B7-976B-E0035FBADB02}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3084" name="Spinner 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3084"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{897A7AF3-3880-4B9D-850D-351E23B9DC65}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Spinner 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{682B7D9F-2901-40F7-8314-F721DAB55923}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="3416300"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Spinner 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1026"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A03D55D2-0445-4BC4-9180-6B48E315FA70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="3784600"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Spinner 3" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1027"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99EBFDA6-888F-44B4-B408-DCF9F7EE35B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="3968750"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Spinner 4" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1028"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5AAD345-A6C8-4BCD-B561-CBA1CE08D268}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="4152900"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Spinner 6" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1030"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3AFC723-7EBE-459D-A935-8F2BC051AE29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="4337050"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3085" name="Spinner 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3085"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8703E23E-5D03-4688-9307-DF98C78A83A2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>6350</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3086" name="Spinner 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3086"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0EAD871-2491-427D-BF79-F6CC0A2ADFBA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3087" name="Spinner 15" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3087"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C906A9FE-EE5A-4BFC-B6AE-3368EE09BCB7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3088" name="Spinner 16" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3088"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B43C7D9-18EA-4E3E-949E-3617E9346425}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3089" name="Spinner 17" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3089"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2DA3AE3-24A9-4092-8CFF-CCEBD7FB6C03}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3090" name="Spinner 18" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3090"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0857F582-6DFE-4E1E-BBEB-86E7D4704B84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>6350</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3091" name="Spinner 19" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4F2BC0-ADB8-47E4-B8A9-E803B5B5E107}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3092" name="Spinner 20" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F52712-1D4A-43C2-B9D0-9FCA4C287B64}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3093" name="Spinner 21" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15BC9E8A-56FF-4ACD-ADC0-CB6A613DCABC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3094" name="Spinner 22" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{821EF44C-02D6-4842-8A4A-7450384AD848}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3095" name="Spinner 23" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3095"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DC7F882-F963-4374-AE94-222CC3AC33BC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3096" name="Spinner 24" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3096"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D81DFC71-F817-421F-B8F7-58DAEFC1100C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3097" name="Spinner 25" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3097"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E31D67D-CEA8-4378-B36F-30424A5205EB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
@@ -2743,30 +5004,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="28">
+      <c r="B2" s="31"/>
+      <c r="C2" s="32">
         <v>45491</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="30"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -3006,16 +5267,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -3169,17 +5430,17 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -3231,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="18">
-        <f>H26-H4</f>
+        <f>H26-0</f>
         <v>0</v>
       </c>
     </row>
@@ -3256,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="18">
-        <f>H27-H10</f>
+        <f t="shared" ref="I27:I30" si="2">H27-0</f>
         <v>0</v>
       </c>
     </row>
@@ -3277,11 +5538,11 @@
         <v>0</v>
       </c>
       <c r="H28" s="16">
-        <f t="shared" ref="H28" si="2">(E28*F28)+G28</f>
+        <f t="shared" ref="H28" si="3">(E28*F28)+G28</f>
         <v>0</v>
       </c>
       <c r="I28" s="18">
-        <f>H28-H10</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3302,11 +5563,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="16">
-        <f t="shared" ref="H29" si="3">(E29*F29)+G29</f>
+        <f t="shared" ref="H29" si="4">(E29*F29)+G29</f>
         <v>0</v>
       </c>
       <c r="I29" s="18">
-        <f>H29-H11</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3327,11 +5588,11 @@
         <v>0</v>
       </c>
       <c r="H30" s="16">
-        <f t="shared" ref="H30" si="4">(E30*F30)+G30</f>
+        <f t="shared" ref="H30" si="5">(E30*F30)+G30</f>
         <v>0</v>
       </c>
       <c r="I30" s="18">
-        <f>H30-H12</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3344,18 +5605,18 @@
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="F33" s="20" t="s">
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="F33" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="22"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="26"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -3365,17 +5626,17 @@
         <f>SUM(H4:H12)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="22">
         <f>B37-B38</f>
         <v>0</v>
       </c>
-      <c r="D34" s="34"/>
+      <c r="D34" s="22"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H34" s="32"/>
-      <c r="I34" s="33"/>
+      <c r="G34" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="20"/>
+      <c r="I34" s="21"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -3385,14 +5646,14 @@
         <f>SUM(H17:H22)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="33"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="21"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -3402,14 +5663,14 @@
         <f>SUM(H26:H30)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="32"/>
-      <c r="I36" s="33"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="21"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -3419,14 +5680,14 @@
         <f>B34+B35+B36</f>
         <v>0</v>
       </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H37" s="32"/>
-      <c r="I37" s="33"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="21"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -3435,8 +5696,8 @@
       <c r="B38" s="6">
         <v>0</v>
       </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3454,11 +5715,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="C34:D38"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="A33:D33"/>
@@ -3466,6 +5722,11 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A24:I24"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="C34:D38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C40" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>
@@ -3502,7 +5763,183 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId7" name="Spinner 22">
+            <control shapeId="1037" r:id="rId7" name="Spinner 13">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1038" r:id="rId8" name="Spinner 14">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>6350</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1040" r:id="rId9" name="Spinner 16">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1041" r:id="rId10" name="Spinner 17">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1042" r:id="rId11" name="Spinner 18">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1043" r:id="rId12" name="Spinner 19">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1044" r:id="rId13" name="Spinner 20">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1045" r:id="rId14" name="Spinner 21">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1046" r:id="rId15" name="Spinner 22">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3524,7 +5961,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1047" r:id="rId8" name="Spinner 23">
+            <control shapeId="1047" r:id="rId16" name="Spinner 23">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3546,19 +5983,19 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1037" r:id="rId9" name="Spinner 13">
+            <control shapeId="1048" r:id="rId17" name="Spinner 24">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>3</xdr:row>
+                    <xdr:row>27</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>4</xdr:row>
+                    <xdr:row>28</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3568,161 +6005,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1038" r:id="rId10" name="Spinner 14">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>6350</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1040" r:id="rId11" name="Spinner 16">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1041" r:id="rId12" name="Spinner 17">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1042" r:id="rId13" name="Spinner 18">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1043" r:id="rId14" name="Spinner 19">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1044" r:id="rId15" name="Spinner 20">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId16" name="Spinner 21">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId17" name="Spinner 57">
+            <control shapeId="1081" r:id="rId18" name="Spinner 57">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3744,7 +6027,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId18" name="Spinner 58">
+            <control shapeId="1082" r:id="rId19" name="Spinner 58">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3766,7 +6049,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId19" name="Spinner 59">
+            <control shapeId="1083" r:id="rId20" name="Spinner 59">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3788,7 +6071,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId20" name="Spinner 60">
+            <control shapeId="1084" r:id="rId21" name="Spinner 60">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3810,7 +6093,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId21" name="Spinner 61">
+            <control shapeId="1085" r:id="rId22" name="Spinner 61">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3832,7 +6115,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId22" name="Spinner 65">
+            <control shapeId="1089" r:id="rId23" name="Spinner 65">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3854,7 +6137,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId23" name="Spinner 66">
+            <control shapeId="1090" r:id="rId24" name="Spinner 66">
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -3868,28 +6151,6 @@
                     <xdr:colOff>184150</xdr:colOff>
                     <xdr:row>18</xdr:row>
                     <xdr:rowOff>6350</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId24" name="Spinner 24">
-              <controlPr defaultSize="0" autoPict="0">
-                <anchor moveWithCells="1" sizeWithCells="1">
-                  <from>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>4</xdr:col>
-                    <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -4032,4 +6293,1502 @@
     </mc:Choice>
   </mc:AlternateContent>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDC6E7F-6BB1-4BA2-AD9F-6F82A2382EBF}">
+  <dimension ref="A1:Q41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.81640625" customWidth="1"/>
+    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="3" max="3" width="6.26953125" customWidth="1"/>
+    <col min="4" max="4" width="4.36328125" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="9.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+    </row>
+    <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="32">
+        <v>45491</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="35"/>
+      <c r="B4" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="45"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="37">
+        <v>1</v>
+      </c>
+      <c r="F4" s="38">
+        <v>145.88999999999999</v>
+      </c>
+      <c r="G4" s="51">
+        <v>2.04</v>
+      </c>
+      <c r="H4" s="16">
+        <f>(E4*F4)+G4</f>
+        <v>147.92999999999998</v>
+      </c>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="35"/>
+      <c r="B5" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="45"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="37">
+        <v>0</v>
+      </c>
+      <c r="F5" s="38">
+        <v>0</v>
+      </c>
+      <c r="G5" s="51">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <f t="shared" ref="H5:H13" si="0">(E5*F5)+G5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="35"/>
+      <c r="B6" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="45"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="37">
+        <v>0</v>
+      </c>
+      <c r="F6" s="38">
+        <v>0</v>
+      </c>
+      <c r="G6" s="51">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" s="35"/>
+      <c r="B7" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="45"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="37">
+        <v>0</v>
+      </c>
+      <c r="F7" s="38">
+        <v>0</v>
+      </c>
+      <c r="G7" s="51">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="35"/>
+      <c r="B8" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="45"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="37">
+        <v>0</v>
+      </c>
+      <c r="F8" s="38">
+        <v>0</v>
+      </c>
+      <c r="G8" s="51">
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="50"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="35"/>
+      <c r="B9" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="37">
+        <v>0</v>
+      </c>
+      <c r="F9" s="38">
+        <v>0</v>
+      </c>
+      <c r="G9" s="51">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="35"/>
+      <c r="B10" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="45"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="37">
+        <v>0</v>
+      </c>
+      <c r="F10" s="38">
+        <v>0</v>
+      </c>
+      <c r="G10" s="51">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="35"/>
+      <c r="B11" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="45"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="37">
+        <v>0</v>
+      </c>
+      <c r="F11" s="38">
+        <v>0</v>
+      </c>
+      <c r="G11" s="51">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
+      <c r="P11" s="53"/>
+      <c r="Q11" s="53"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="35"/>
+      <c r="B12" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="37">
+        <v>0</v>
+      </c>
+      <c r="F12" s="38">
+        <v>0</v>
+      </c>
+      <c r="G12" s="51">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="35"/>
+      <c r="B13" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="37">
+        <v>0</v>
+      </c>
+      <c r="F13" s="38">
+        <v>0</v>
+      </c>
+      <c r="G13" s="51">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A17" s="35"/>
+      <c r="B17" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="45"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="37">
+        <v>0</v>
+      </c>
+      <c r="F17" s="38">
+        <v>0</v>
+      </c>
+      <c r="G17" s="51">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16">
+        <f>(E17*F17)+G17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="35"/>
+      <c r="B18" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="45"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="37">
+        <v>0</v>
+      </c>
+      <c r="F18" s="38">
+        <v>0</v>
+      </c>
+      <c r="G18" s="51">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>0</v>
+      </c>
+      <c r="K18" s="44"/>
+      <c r="L18" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A19" s="35"/>
+      <c r="B19" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="45"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="37">
+        <v>0</v>
+      </c>
+      <c r="F19" s="38">
+        <v>0</v>
+      </c>
+      <c r="G19" s="51">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <f t="shared" ref="H19:H22" si="1">(E19*F19)+G19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" s="35"/>
+      <c r="B20" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="45"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="37">
+        <v>0</v>
+      </c>
+      <c r="F20" s="38">
+        <v>0</v>
+      </c>
+      <c r="G20" s="51">
+        <v>0</v>
+      </c>
+      <c r="H20" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A21" s="35"/>
+      <c r="B21" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="45"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="37">
+        <v>0</v>
+      </c>
+      <c r="F21" s="38">
+        <v>0</v>
+      </c>
+      <c r="G21" s="51">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="35"/>
+      <c r="B22" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="37">
+        <v>0</v>
+      </c>
+      <c r="F22" s="38">
+        <v>0</v>
+      </c>
+      <c r="G22" s="51">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="K24" s="59" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="59"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="59"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="59"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="61"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A26" s="35"/>
+      <c r="B26" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="37">
+        <v>0</v>
+      </c>
+      <c r="F26" s="39">
+        <v>0</v>
+      </c>
+      <c r="G26" s="51">
+        <v>0</v>
+      </c>
+      <c r="H26" s="16">
+        <f>(E26*F26)+G26</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="54">
+        <f>H26-H4</f>
+        <v>-147.92999999999998</v>
+      </c>
+      <c r="K26" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="63"/>
+      <c r="P26" s="63"/>
+      <c r="Q26" s="64"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27" s="35"/>
+      <c r="B27" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="37">
+        <v>0</v>
+      </c>
+      <c r="F27" s="38">
+        <v>0</v>
+      </c>
+      <c r="G27" s="51">
+        <v>0</v>
+      </c>
+      <c r="H27" s="16">
+        <f>(E27*F27)+G27</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="54">
+        <f t="shared" ref="I27:I30" si="2">H27-0</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="65"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28" s="35"/>
+      <c r="B28" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="37">
+        <v>0</v>
+      </c>
+      <c r="F28" s="38">
+        <v>0</v>
+      </c>
+      <c r="G28" s="51">
+        <v>0</v>
+      </c>
+      <c r="H28" s="16">
+        <f t="shared" ref="H28:H30" si="3">(E28*F28)+G28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="65"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29" s="35"/>
+      <c r="B29" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="37">
+        <v>0</v>
+      </c>
+      <c r="F29" s="38">
+        <v>0</v>
+      </c>
+      <c r="G29" s="51">
+        <v>0</v>
+      </c>
+      <c r="H29" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="54">
+        <f>H29-0</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="65"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A30" s="35"/>
+      <c r="B30" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="45"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="37">
+        <v>0</v>
+      </c>
+      <c r="F30" s="38">
+        <v>0</v>
+      </c>
+      <c r="G30" s="51">
+        <v>0</v>
+      </c>
+      <c r="H30" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="65"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C31" s="4"/>
+      <c r="I31" s="5"/>
+      <c r="K31" s="66" t="s">
+        <v>69</v>
+      </c>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="68"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C32" s="4"/>
+      <c r="I32" s="5"/>
+      <c r="K32" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="71"/>
+    </row>
+    <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="F33" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="26"/>
+    </row>
+    <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="20"/>
+      <c r="I34" s="21"/>
+    </row>
+    <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="20"/>
+      <c r="I35" s="21"/>
+    </row>
+    <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" s="20"/>
+      <c r="I36" s="21"/>
+    </row>
+    <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" s="20"/>
+      <c r="I37" s="21"/>
+    </row>
+    <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+    </row>
+    <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="L17:Q17"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="K7:Q7"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:I33"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C40" r:id="rId1" xr:uid="{DEFCB1FC-5A4C-4669-B8BE-6F0E263F6A35}"/>
+    <hyperlink ref="B41" r:id="rId2" xr:uid="{78848BD0-6725-459B-9B8C-D0DAFE5DE5B5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3073" r:id="rId6" name="Spinner 1">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3075" r:id="rId7" name="Spinner 3">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>6350</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3076" r:id="rId8" name="Spinner 4">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3077" r:id="rId9" name="Spinner 5">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3078" r:id="rId10" name="Spinner 6">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3079" r:id="rId11" name="Spinner 7">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3080" r:id="rId12" name="Spinner 8">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3081" r:id="rId13" name="Spinner 9">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3082" r:id="rId14" name="Spinner 10">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3083" r:id="rId15" name="Spinner 11">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3084" r:id="rId16" name="Spinner 12">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3085" r:id="rId17" name="Spinner 13">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3086" r:id="rId18" name="Spinner 14">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>6350</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3087" r:id="rId19" name="Spinner 15">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3088" r:id="rId20" name="Spinner 16">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3089" r:id="rId21" name="Spinner 17">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3090" r:id="rId22" name="Spinner 18">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3091" r:id="rId23" name="Spinner 19">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>6350</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3092" r:id="rId24" name="Spinner 20">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3093" r:id="rId25" name="Spinner 21">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3094" r:id="rId26" name="Spinner 22">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3095" r:id="rId27" name="Spinner 23">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3096" r:id="rId28" name="Spinner 24">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3097" r:id="rId29" name="Spinner 25">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="3074" r:id="rId30" name="Spinner 2">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
 </file>
--- a/assets/downloads/CONFIG MAKER by KJ.xlsx
+++ b/assets/downloads/CONFIG MAKER by KJ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/kevin_jamet_epita_fr/Documents/Others/Configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1214" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E9BE963-031D-4AC8-9EE5-52301470B6A1}"/>
+  <xr:revisionPtr revIDLastSave="1259" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6317D1E7-08B5-4C34-8C50-3375E62A927C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8947F335-7243-4BC9-9D88-00188AB47FC0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="74">
   <si>
     <t>En stock</t>
   </si>
@@ -257,15 +257,19 @@
   <si>
     <t>Prix total du produit, quantité et livraison appliquée</t>
   </si>
+  <si>
+    <t>CONFIG MAKER v2024.7.29</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[Red]\▲\ 0.00;[Green]\ \▼\ 0.00"/>
+    <numFmt numFmtId="165" formatCode="[Red]\▲\ 0.00;[Color50]\ \▼\ 0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,8 +351,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -442,6 +454,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -591,7 +609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,7 +650,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -681,84 +716,10 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -770,12 +731,146 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2851,7 +2946,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61FB5EC9-F771-4B7C-A55C-237BAE44ADFC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2896,7 +2991,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1026"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C866209-3260-4185-8693-9387161461EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2941,7 +3036,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1027"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B10C7B63-5AD6-48C0-9D28-5335519348E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2986,7 +3081,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1028"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDC1279E-7E1D-4698-809E-1B9416F4595A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3031,7 +3126,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1029"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{984C00EA-6C19-4288-96E1-EB0AD3C81C28}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3076,7 +3171,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1030"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{153DEF4E-B7E5-412D-8A32-DD74AF9C9EA6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3121,7 +3216,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1031"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBF7788E-BFD3-46A7-837B-348745FE4736}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3166,7 +3261,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1032"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAB7DCDA-D72E-4BD0-9782-15756A480B9F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3213,7 +3308,7 @@
                   <a14:compatExt spid="_x0000_s3073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54289062-98E0-45D0-A26D-D866DC5C8188}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000010C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3263,7 +3358,7 @@
                   <a14:compatExt spid="_x0000_s3074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D82B1CAB-137A-44A7-A8F9-648A63FE8EB7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000020C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3313,7 +3408,7 @@
                   <a14:compatExt spid="_x0000_s3075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D314E8DF-357B-4856-8E54-B73378E08F68}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000030C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3363,7 +3458,7 @@
                   <a14:compatExt spid="_x0000_s3076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C75111DE-F527-4375-9E0A-8E0B5B9ADECA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000040C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3413,7 +3508,7 @@
                   <a14:compatExt spid="_x0000_s3077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C97EE75-F7E8-4E78-86F1-411B4A51A5B9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000050C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3463,7 +3558,7 @@
                   <a14:compatExt spid="_x0000_s3078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D69533A8-1F6B-42A5-847A-287A5C67DAB0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000060C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3513,7 +3608,7 @@
                   <a14:compatExt spid="_x0000_s3079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7942FBE8-149D-4C22-B6D1-E2BD07CDC689}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000070C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3563,7 +3658,7 @@
                   <a14:compatExt spid="_x0000_s3080"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42AD6690-5C19-4AE4-8C84-227443DE9D4A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000080C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3613,7 +3708,7 @@
                   <a14:compatExt spid="_x0000_s3081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BDCECBC-150A-4C3B-9367-D1AC7741F971}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000090C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3663,7 +3758,7 @@
                   <a14:compatExt spid="_x0000_s3082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EACE3175-F8E0-41D3-8A5C-82BBA8E16570}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3713,7 +3808,7 @@
                   <a14:compatExt spid="_x0000_s3083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6EA0CA8-A7B6-47B7-976B-E0035FBADB02}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3763,7 +3858,7 @@
                   <a14:compatExt spid="_x0000_s3084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{897A7AF3-3880-4B9D-850D-351E23B9DC65}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3811,7 +3906,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{682B7D9F-2901-40F7-8314-F721DAB55923}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3856,7 +3951,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1026"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A03D55D2-0445-4BC4-9180-6B48E315FA70}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3901,7 +3996,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1027"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99EBFDA6-888F-44B4-B408-DCF9F7EE35B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3946,7 +4041,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1028"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5AAD345-A6C8-4BCD-B561-CBA1CE08D268}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3991,7 +4086,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1030"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3AFC723-7EBE-459D-A935-8F2BC051AE29}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4038,7 +4133,7 @@
                   <a14:compatExt spid="_x0000_s3085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8703E23E-5D03-4688-9307-DF98C78A83A2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4088,7 +4183,7 @@
                   <a14:compatExt spid="_x0000_s3086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0EAD871-2491-427D-BF79-F6CC0A2ADFBA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4138,7 +4233,7 @@
                   <a14:compatExt spid="_x0000_s3087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C906A9FE-EE5A-4BFC-B6AE-3368EE09BCB7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F0C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4188,7 +4283,7 @@
                   <a14:compatExt spid="_x0000_s3088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B43C7D9-18EA-4E3E-949E-3617E9346425}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000100C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4238,7 +4333,7 @@
                   <a14:compatExt spid="_x0000_s3089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2DA3AE3-24A9-4092-8CFF-CCEBD7FB6C03}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000110C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4288,7 +4383,7 @@
                   <a14:compatExt spid="_x0000_s3090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0857F582-6DFE-4E1E-BBEB-86E7D4704B84}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000120C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4338,7 +4433,7 @@
                   <a14:compatExt spid="_x0000_s3091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4F2BC0-ADB8-47E4-B8A9-E803B5B5E107}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000130C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4388,7 +4483,7 @@
                   <a14:compatExt spid="_x0000_s3092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F52712-1D4A-43C2-B9D0-9FCA4C287B64}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000140C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4438,7 +4533,7 @@
                   <a14:compatExt spid="_x0000_s3093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15BC9E8A-56FF-4ACD-ADC0-CB6A613DCABC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000150C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4488,7 +4583,7 @@
                   <a14:compatExt spid="_x0000_s3094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{821EF44C-02D6-4842-8A4A-7450384AD848}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000160C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4538,7 +4633,7 @@
                   <a14:compatExt spid="_x0000_s3095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DC7F882-F963-4374-AE94-222CC3AC33BC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000170C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4588,7 +4683,7 @@
                   <a14:compatExt spid="_x0000_s3096"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D81DFC71-F817-421F-B8F7-58DAEFC1100C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000180C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4638,7 +4733,7 @@
                   <a14:compatExt spid="_x0000_s3097"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E31D67D-CEA8-4378-B36F-30424A5205EB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000190C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4666,10 +4761,6 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5004,30 +5095,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="32">
-        <v>45491</v>
-      </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45">
+        <v>45502</v>
+      </c>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5267,16 +5358,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -5430,17 +5521,17 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -5491,7 +5582,7 @@
         <f>(E26*F26)+G26</f>
         <v>0</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="30">
         <f>H26-0</f>
         <v>0</v>
       </c>
@@ -5516,8 +5607,8 @@
         <f>(E27*F27)+G27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="18">
-        <f t="shared" ref="I27:I30" si="2">H27-0</f>
+      <c r="I27" s="30">
+        <f>H27-0</f>
         <v>0</v>
       </c>
     </row>
@@ -5538,11 +5629,11 @@
         <v>0</v>
       </c>
       <c r="H28" s="16">
-        <f t="shared" ref="H28" si="3">(E28*F28)+G28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H28" si="2">(E28*F28)+G28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="30">
+        <f t="shared" ref="I28:I30" si="3">H28-0</f>
         <v>0</v>
       </c>
     </row>
@@ -5566,8 +5657,8 @@
         <f t="shared" ref="H29" si="4">(E29*F29)+G29</f>
         <v>0</v>
       </c>
-      <c r="I29" s="18">
-        <f t="shared" si="2"/>
+      <c r="I29" s="30">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5591,8 +5682,8 @@
         <f t="shared" ref="H30" si="5">(E30*F30)+G30</f>
         <v>0</v>
       </c>
-      <c r="I30" s="18">
-        <f t="shared" si="2"/>
+      <c r="I30" s="30">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5605,18 +5696,18 @@
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="F33" s="24" t="s">
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="F33" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="26"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="39"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -5626,17 +5717,17 @@
         <f>SUM(H4:H12)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="35">
         <f>B37-B38</f>
         <v>0</v>
       </c>
-      <c r="D34" s="22"/>
+      <c r="D34" s="35"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="H34" s="20"/>
-      <c r="I34" s="21"/>
+      <c r="G34" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="33"/>
+      <c r="I34" s="34"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -5646,14 +5737,14 @@
         <f>SUM(H17:H22)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="19" t="s">
+      <c r="G35" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="21"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="34"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -5663,46 +5754,46 @@
         <f>SUM(H26:H30)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="19" t="s">
+      <c r="G36" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="20"/>
-      <c r="I36" s="21"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="34"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="29">
         <f>B34+B35+B36</f>
         <v>0</v>
       </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="19" t="s">
+      <c r="G37" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="H37" s="20"/>
-      <c r="I37" s="21"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="34"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="6">
-        <v>0</v>
-      </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
+      <c r="B38" s="31">
+        <v>0</v>
+      </c>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="14" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>40</v>
@@ -5728,6 +5819,29 @@
     <mergeCell ref="G34:I34"/>
     <mergeCell ref="C34:D38"/>
   </mergeCells>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
+      <formula>$B$38</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
+      <formula>$B$38</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>$B$38</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+      <formula>$B$38</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="greaterThan">
+      <formula>$B$38</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
+      <formula>$B$38</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C40" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>
     <hyperlink ref="B41" r:id="rId2" xr:uid="{BB511D4F-6DFD-4166-91EE-2B5D78AF6761}"/>
@@ -6312,30 +6426,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="32">
+      <c r="B2" s="44"/>
+      <c r="C2" s="45">
         <v>45491</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6362,268 +6476,268 @@
       <c r="H3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="40" t="s">
+      <c r="K3" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="37">
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="20">
         <v>1</v>
       </c>
-      <c r="F4" s="38">
+      <c r="F4" s="21">
         <v>145.88999999999999</v>
       </c>
-      <c r="G4" s="51">
+      <c r="G4" s="27">
         <v>2.04</v>
       </c>
       <c r="H4" s="16">
         <f>(E4*F4)+G4</f>
         <v>147.92999999999998</v>
       </c>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5" s="35"/>
-      <c r="B5" s="36" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="37">
-        <v>0</v>
-      </c>
-      <c r="F5" s="38">
-        <v>0</v>
-      </c>
-      <c r="G5" s="51">
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="20">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <v>0</v>
+      </c>
+      <c r="G5" s="27">
         <v>0</v>
       </c>
       <c r="H5" s="16">
         <f t="shared" ref="H5:H13" si="0">(E5*F5)+G5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" s="35"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="37">
-        <v>0</v>
-      </c>
-      <c r="F6" s="38">
-        <v>0</v>
-      </c>
-      <c r="G6" s="51">
+      <c r="C6" s="24"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="20">
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <v>0</v>
+      </c>
+      <c r="G6" s="27">
         <v>0</v>
       </c>
       <c r="H6" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7" s="35"/>
-      <c r="B7" s="36" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="37">
-        <v>0</v>
-      </c>
-      <c r="F7" s="38">
-        <v>0</v>
-      </c>
-      <c r="G7" s="51">
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <v>0</v>
+      </c>
+      <c r="G7" s="27">
         <v>0</v>
       </c>
       <c r="H7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="52" t="s">
+      <c r="K7" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="60"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="60"/>
+      <c r="Q7" s="60"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="35"/>
-      <c r="B8" s="36" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="37">
-        <v>0</v>
-      </c>
-      <c r="F8" s="38">
-        <v>0</v>
-      </c>
-      <c r="G8" s="51">
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="20">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0</v>
+      </c>
+      <c r="G8" s="27">
         <v>0</v>
       </c>
       <c r="H8" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="50" t="s">
+      <c r="K8" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="50"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="35"/>
-      <c r="B9" s="36" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="37">
-        <v>0</v>
-      </c>
-      <c r="F9" s="38">
-        <v>0</v>
-      </c>
-      <c r="G9" s="51">
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="20">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
+        <v>0</v>
+      </c>
+      <c r="G9" s="27">
         <v>0</v>
       </c>
       <c r="H9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="46" t="s">
+      <c r="K9" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="65"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="37">
-        <v>0</v>
-      </c>
-      <c r="F10" s="38">
-        <v>0</v>
-      </c>
-      <c r="G10" s="51">
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="20">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21">
+        <v>0</v>
+      </c>
+      <c r="G10" s="27">
         <v>0</v>
       </c>
       <c r="H10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="37">
-        <v>0</v>
-      </c>
-      <c r="F11" s="38">
-        <v>0</v>
-      </c>
-      <c r="G11" s="51">
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="20">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0</v>
+      </c>
+      <c r="G11" s="27">
         <v>0</v>
       </c>
       <c r="H11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="53" t="s">
+      <c r="K11" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="37">
-        <v>0</v>
-      </c>
-      <c r="F12" s="38">
-        <v>0</v>
-      </c>
-      <c r="G12" s="51">
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="20">
+        <v>0</v>
+      </c>
+      <c r="F12" s="21">
+        <v>0</v>
+      </c>
+      <c r="G12" s="27">
         <v>0</v>
       </c>
       <c r="H12" s="16">
@@ -6632,19 +6746,19 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13" s="35"/>
-      <c r="B13" s="36" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="37">
-        <v>0</v>
-      </c>
-      <c r="F13" s="38">
-        <v>0</v>
-      </c>
-      <c r="G13" s="51">
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="20">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21">
+        <v>0</v>
+      </c>
+      <c r="G13" s="27">
         <v>0</v>
       </c>
       <c r="H13" s="16">
@@ -6653,16 +6767,16 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -6692,19 +6806,19 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A17" s="35"/>
-      <c r="B17" s="36" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="37">
-        <v>0</v>
-      </c>
-      <c r="F17" s="38">
-        <v>0</v>
-      </c>
-      <c r="G17" s="51">
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="20">
+        <v>0</v>
+      </c>
+      <c r="F17" s="21">
+        <v>0</v>
+      </c>
+      <c r="G17" s="27">
         <v>0</v>
       </c>
       <c r="H17" s="16">
@@ -6712,58 +6826,58 @@
         <v>0</v>
       </c>
       <c r="K17" s="16"/>
-      <c r="L17" s="57" t="s">
+      <c r="L17" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="M17" s="57"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="57"/>
-      <c r="P17" s="57"/>
-      <c r="Q17" s="57"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A18" s="35"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="18"/>
+      <c r="B18" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="37">
-        <v>0</v>
-      </c>
-      <c r="F18" s="38">
-        <v>0</v>
-      </c>
-      <c r="G18" s="51">
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="20">
+        <v>0</v>
+      </c>
+      <c r="F18" s="21">
+        <v>0</v>
+      </c>
+      <c r="G18" s="27">
         <v>0</v>
       </c>
       <c r="H18" s="16">
         <v>0</v>
       </c>
-      <c r="K18" s="44"/>
-      <c r="L18" s="57" t="s">
+      <c r="K18" s="23"/>
+      <c r="L18" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="57"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="49"/>
+      <c r="O18" s="49"/>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="49"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A19" s="35"/>
-      <c r="B19" s="36" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="37">
-        <v>0</v>
-      </c>
-      <c r="F19" s="38">
-        <v>0</v>
-      </c>
-      <c r="G19" s="51">
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="20">
+        <v>0</v>
+      </c>
+      <c r="F19" s="21">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27">
         <v>0</v>
       </c>
       <c r="H19" s="16">
@@ -6772,19 +6886,19 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A20" s="35"/>
-      <c r="B20" s="36" t="s">
+      <c r="A20" s="18"/>
+      <c r="B20" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="37">
-        <v>0</v>
-      </c>
-      <c r="F20" s="38">
-        <v>0</v>
-      </c>
-      <c r="G20" s="51">
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="21">
+        <v>0</v>
+      </c>
+      <c r="G20" s="27">
         <v>0</v>
       </c>
       <c r="H20" s="16">
@@ -6792,19 +6906,19 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A21" s="35"/>
-      <c r="B21" s="36" t="s">
+      <c r="A21" s="18"/>
+      <c r="B21" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="37">
-        <v>0</v>
-      </c>
-      <c r="F21" s="38">
-        <v>0</v>
-      </c>
-      <c r="G21" s="51">
+      <c r="C21" s="24"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="20">
+        <v>0</v>
+      </c>
+      <c r="F21" s="21">
+        <v>0</v>
+      </c>
+      <c r="G21" s="27">
         <v>0</v>
       </c>
       <c r="H21" s="16">
@@ -6813,19 +6927,19 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A22" s="35"/>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="18"/>
+      <c r="B22" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="37">
-        <v>0</v>
-      </c>
-      <c r="F22" s="38">
-        <v>0</v>
-      </c>
-      <c r="G22" s="51">
+      <c r="C22" s="24"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="20">
+        <v>0</v>
+      </c>
+      <c r="F22" s="21">
+        <v>0</v>
+      </c>
+      <c r="G22" s="27">
         <v>0</v>
       </c>
       <c r="H22" s="16">
@@ -6834,26 +6948,26 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="K24" s="59" t="s">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="K24" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="L24" s="59"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="59"/>
-      <c r="O24" s="59"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="59"/>
+      <c r="L24" s="66"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="66"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="66"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -6883,225 +6997,225 @@
       <c r="I25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K25" s="60" t="s">
+      <c r="K25" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="61"/>
+      <c r="L25" s="68"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="68"/>
+      <c r="Q25" s="69"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36" t="s">
+      <c r="A26" s="18"/>
+      <c r="B26" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="37">
-        <v>0</v>
-      </c>
-      <c r="F26" s="39">
-        <v>0</v>
-      </c>
-      <c r="G26" s="51">
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="20">
+        <v>0</v>
+      </c>
+      <c r="F26" s="22">
+        <v>0</v>
+      </c>
+      <c r="G26" s="27">
         <v>0</v>
       </c>
       <c r="H26" s="16">
         <f>(E26*F26)+G26</f>
         <v>0</v>
       </c>
-      <c r="I26" s="54">
+      <c r="I26" s="28">
         <f>H26-H4</f>
         <v>-147.92999999999998</v>
       </c>
-      <c r="K26" s="62" t="s">
+      <c r="K26" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="64"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="71"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="72"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36" t="s">
+      <c r="A27" s="18"/>
+      <c r="B27" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="37">
-        <v>0</v>
-      </c>
-      <c r="F27" s="38">
-        <v>0</v>
-      </c>
-      <c r="G27" s="51">
+      <c r="C27" s="24"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="20">
+        <v>0</v>
+      </c>
+      <c r="F27" s="21">
+        <v>0</v>
+      </c>
+      <c r="G27" s="27">
         <v>0</v>
       </c>
       <c r="H27" s="16">
         <f>(E27*F27)+G27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="54">
+      <c r="I27" s="28">
         <f t="shared" ref="I27:I30" si="2">H27-0</f>
         <v>0</v>
       </c>
-      <c r="K27" s="56" t="s">
+      <c r="K27" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="65"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="55"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28" s="35"/>
-      <c r="B28" s="36" t="s">
+      <c r="A28" s="18"/>
+      <c r="B28" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="37">
-        <v>0</v>
-      </c>
-      <c r="F28" s="38">
-        <v>0</v>
-      </c>
-      <c r="G28" s="51">
+      <c r="C28" s="24"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="20">
+        <v>0</v>
+      </c>
+      <c r="F28" s="21">
+        <v>0</v>
+      </c>
+      <c r="G28" s="27">
         <v>0</v>
       </c>
       <c r="H28" s="16">
         <f t="shared" ref="H28:H30" si="3">(E28*F28)+G28</f>
         <v>0</v>
       </c>
-      <c r="I28" s="54">
+      <c r="I28" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K28" s="56" t="s">
+      <c r="K28" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="65"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="55"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A29" s="35"/>
-      <c r="B29" s="36" t="s">
+      <c r="A29" s="18"/>
+      <c r="B29" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="37">
-        <v>0</v>
-      </c>
-      <c r="F29" s="38">
-        <v>0</v>
-      </c>
-      <c r="G29" s="51">
+      <c r="C29" s="24"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="20">
+        <v>0</v>
+      </c>
+      <c r="F29" s="21">
+        <v>0</v>
+      </c>
+      <c r="G29" s="27">
         <v>0</v>
       </c>
       <c r="H29" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I29" s="54">
+      <c r="I29" s="28">
         <f>H29-0</f>
         <v>0</v>
       </c>
-      <c r="K29" s="56" t="s">
+      <c r="K29" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="65"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="55"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A30" s="35"/>
-      <c r="B30" s="36" t="s">
+      <c r="A30" s="18"/>
+      <c r="B30" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="37">
-        <v>0</v>
-      </c>
-      <c r="F30" s="38">
-        <v>0</v>
-      </c>
-      <c r="G30" s="51">
+      <c r="C30" s="24"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="20">
+        <v>0</v>
+      </c>
+      <c r="F30" s="21">
+        <v>0</v>
+      </c>
+      <c r="G30" s="27">
         <v>0</v>
       </c>
       <c r="H30" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I30" s="54">
+      <c r="I30" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K30" s="56" t="s">
+      <c r="K30" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="58"/>
-      <c r="O30" s="58"/>
-      <c r="P30" s="58"/>
-      <c r="Q30" s="65"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="55"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C31" s="4"/>
       <c r="I31" s="5"/>
-      <c r="K31" s="66" t="s">
+      <c r="K31" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="67"/>
-      <c r="Q31" s="68"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="63"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C32" s="4"/>
       <c r="I32" s="5"/>
-      <c r="K32" s="69" t="s">
+      <c r="K32" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="L32" s="70"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="70"/>
-      <c r="O32" s="70"/>
-      <c r="P32" s="70"/>
-      <c r="Q32" s="71"/>
+      <c r="L32" s="51"/>
+      <c r="M32" s="51"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="51"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="52"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="F33" s="24" t="s">
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="F33" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="26"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="39"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -7110,14 +7224,14 @@
       <c r="B34" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="H34" s="20"/>
-      <c r="I34" s="21"/>
+      <c r="G34" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="33"/>
+      <c r="I34" s="34"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -7126,14 +7240,14 @@
       <c r="B35" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="19" t="s">
+      <c r="G35" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="21"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="34"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -7142,14 +7256,14 @@
       <c r="B36" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="19" t="s">
+      <c r="G36" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="20"/>
-      <c r="I36" s="21"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="34"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -7158,14 +7272,14 @@
       <c r="B37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="19" t="s">
+      <c r="G37" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="H37" s="20"/>
-      <c r="I37" s="21"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="34"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -7174,8 +7288,8 @@
       <c r="B38" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7193,38 +7307,38 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="K11:Q11"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="L17:Q17"/>
-    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="K10:Q10"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="K6:Q6"/>
     <mergeCell ref="K7:Q7"/>
-    <mergeCell ref="K8:Q8"/>
-    <mergeCell ref="K9:Q9"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="K10:Q10"/>
     <mergeCell ref="C34:D38"/>
     <mergeCell ref="G34:I34"/>
     <mergeCell ref="G35:I35"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="G37:I37"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="L17:Q17"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="K31:Q31"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="F33:I33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C40" r:id="rId1" xr:uid="{DEFCB1FC-5A4C-4669-B8BE-6F0E263F6A35}"/>

--- a/assets/downloads/CONFIG MAKER by KJ.xlsx
+++ b/assets/downloads/CONFIG MAKER by KJ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/kevin_jamet_epita_fr/Documents/Others/Configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1259" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6317D1E7-08B5-4C34-8C50-3375E62A927C}"/>
+  <xr:revisionPtr revIDLastSave="1274" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37ADE882-34C1-457B-BDB7-AD1171C99C3A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8947F335-7243-4BC9-9D88-00188AB47FC0}"/>
   </bookViews>
@@ -258,7 +258,7 @@
     <t>Prix total du produit, quantité et livraison appliquée</t>
   </si>
   <si>
-    <t>CONFIG MAKER v2024.7.29</t>
+    <t>CONFIG MAKER v2024.8.9</t>
   </si>
 </sst>
 </file>
@@ -668,18 +668,6 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -716,19 +704,22 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -738,36 +729,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -792,6 +753,45 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4763,6 +4763,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5085,8 +5089,7 @@
   <cols>
     <col min="1" max="1" width="5.81640625" customWidth="1"/>
     <col min="2" max="2" width="56" customWidth="1"/>
-    <col min="3" max="3" width="6.26953125" customWidth="1"/>
-    <col min="4" max="4" width="4.36328125" customWidth="1"/>
+    <col min="3" max="4" width="6.6328125" customWidth="1"/>
     <col min="5" max="5" width="10.08984375" customWidth="1"/>
     <col min="6" max="6" width="9.90625" customWidth="1"/>
     <col min="7" max="7" width="9.1796875" customWidth="1"/>
@@ -5095,30 +5098,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45">
-        <v>45502</v>
-      </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="47"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41">
+        <v>45513</v>
+      </c>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5358,16 +5361,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -5521,17 +5524,17 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -5696,18 +5699,18 @@
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="F33" s="37" t="s">
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="F33" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="39"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="35"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -5717,17 +5720,17 @@
         <f>SUM(H4:H12)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="47">
         <f>B37-B38</f>
         <v>0</v>
       </c>
-      <c r="D34" s="35"/>
+      <c r="D34" s="47"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H34" s="33"/>
-      <c r="I34" s="34"/>
+      <c r="G34" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="45"/>
+      <c r="I34" s="46"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -5737,14 +5740,14 @@
         <f>SUM(H17:H22)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="33"/>
-      <c r="I35" s="34"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="46"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -5754,14 +5757,14 @@
         <f>SUM(H26:H30)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="33"/>
-      <c r="I36" s="34"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="46"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -5771,14 +5774,14 @@
         <f>B34+B35+B36</f>
         <v>0</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="H37" s="33"/>
-      <c r="I37" s="34"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="46"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -5787,8 +5790,8 @@
       <c r="B38" s="31">
         <v>0</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5806,6 +5809,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="C34:D38"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="A33:D33"/>
@@ -5813,11 +5821,6 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="C34:D38"/>
   </mergeCells>
   <conditionalFormatting sqref="B37">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
@@ -6426,30 +6429,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45">
+      <c r="B2" s="40"/>
+      <c r="C2" s="41">
         <v>45491</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="47"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6476,15 +6479,15 @@
       <c r="H3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="18"/>
@@ -6506,13 +6509,13 @@
         <f>(E4*F4)+G4</f>
         <v>147.92999999999998</v>
       </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="57"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="18"/>
@@ -6534,15 +6537,15 @@
         <f t="shared" ref="H5:H13" si="0">(E5*F5)+G5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="58" t="s">
+      <c r="K5" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="18"/>
@@ -6564,15 +6567,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="59" t="s">
+      <c r="K6" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
@@ -6594,15 +6597,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
@@ -6624,15 +6627,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="64" t="s">
+      <c r="K8" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
@@ -6654,15 +6657,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="65" t="s">
+      <c r="K9" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="65"/>
-      <c r="M9" s="65"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="65"/>
-      <c r="P9" s="65"/>
-      <c r="Q9" s="65"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
@@ -6684,15 +6687,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="73" t="s">
+      <c r="K10" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="L10" s="73"/>
-      <c r="M10" s="73"/>
-      <c r="N10" s="73"/>
-      <c r="O10" s="73"/>
-      <c r="P10" s="73"/>
-      <c r="Q10" s="73"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="60"/>
+      <c r="N10" s="60"/>
+      <c r="O10" s="60"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="18"/>
@@ -6714,15 +6717,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="48" t="s">
+      <c r="K11" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="48"/>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="48"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="66"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="66"/>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="66"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="18"/>
@@ -6767,16 +6770,16 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -6826,14 +6829,14 @@
         <v>0</v>
       </c>
       <c r="K17" s="16"/>
-      <c r="L17" s="49" t="s">
+      <c r="L17" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="49"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="18"/>
@@ -6855,14 +6858,14 @@
         <v>0</v>
       </c>
       <c r="K18" s="23"/>
-      <c r="L18" s="49" t="s">
+      <c r="L18" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
-      <c r="O18" s="49"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="49"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="18"/>
@@ -6948,26 +6951,26 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="K24" s="66" t="s">
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="K24" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -6997,15 +7000,15 @@
       <c r="I25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K25" s="67" t="s">
+      <c r="K25" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="69"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="55"/>
+      <c r="Q25" s="56"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="18"/>
@@ -7031,15 +7034,15 @@
         <f>H26-H4</f>
         <v>-147.92999999999998</v>
       </c>
-      <c r="K26" s="70" t="s">
+      <c r="K26" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="72"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="59"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="18"/>
@@ -7065,15 +7068,15 @@
         <f t="shared" ref="I27:I30" si="2">H27-0</f>
         <v>0</v>
       </c>
-      <c r="K27" s="53" t="s">
+      <c r="K27" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="55"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="52"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="18"/>
@@ -7099,15 +7102,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K28" s="53" t="s">
+      <c r="K28" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="L28" s="54"/>
-      <c r="M28" s="54"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="55"/>
+      <c r="L28" s="51"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="51"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="52"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="18"/>
@@ -7133,15 +7136,15 @@
         <f>H29-0</f>
         <v>0</v>
       </c>
-      <c r="K29" s="53" t="s">
+      <c r="K29" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="55"/>
+      <c r="L29" s="51"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="51"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="52"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="18"/>
@@ -7167,55 +7170,55 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K30" s="53" t="s">
+      <c r="K30" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="L30" s="54"/>
-      <c r="M30" s="54"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="54"/>
-      <c r="P30" s="54"/>
-      <c r="Q30" s="55"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="51"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="51"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="52"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C31" s="4"/>
       <c r="I31" s="5"/>
-      <c r="K31" s="61" t="s">
+      <c r="K31" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="L31" s="62"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="62"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="63"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="73"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C32" s="4"/>
       <c r="I32" s="5"/>
-      <c r="K32" s="50" t="s">
+      <c r="K32" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="L32" s="51"/>
-      <c r="M32" s="51"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="52"/>
+      <c r="L32" s="69"/>
+      <c r="M32" s="69"/>
+      <c r="N32" s="69"/>
+      <c r="O32" s="69"/>
+      <c r="P32" s="69"/>
+      <c r="Q32" s="70"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="F33" s="37" t="s">
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="F33" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="39"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="35"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -7224,14 +7227,14 @@
       <c r="B34" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H34" s="33"/>
-      <c r="I34" s="34"/>
+      <c r="G34" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" s="45"/>
+      <c r="I34" s="46"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -7240,14 +7243,14 @@
       <c r="B35" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="33"/>
-      <c r="I35" s="34"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="46"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -7256,14 +7259,14 @@
       <c r="B36" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="33"/>
-      <c r="I36" s="34"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="46"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -7272,14 +7275,14 @@
       <c r="B37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="H37" s="33"/>
-      <c r="I37" s="34"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="46"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -7288,8 +7291,8 @@
       <c r="B38" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7307,6 +7310,29 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="L17:Q17"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="K8:Q8"/>
     <mergeCell ref="K9:Q9"/>
     <mergeCell ref="K27:Q27"/>
@@ -7316,29 +7342,6 @@
     <mergeCell ref="K25:Q25"/>
     <mergeCell ref="K26:Q26"/>
     <mergeCell ref="K10:Q10"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="K6:Q6"/>
-    <mergeCell ref="K7:Q7"/>
-    <mergeCell ref="C34:D38"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="K11:Q11"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="L17:Q17"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C40" r:id="rId1" xr:uid="{DEFCB1FC-5A4C-4669-B8BE-6F0E263F6A35}"/>
